--- a/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
+++ b/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,46 +409,32 @@
       <c r="C1" t="str">
         <v>TimeStamp</v>
       </c>
-      <c r="D1" t="str">
-        <v>Timestamp</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>User LEAD PM melakukan akses ke menu Stip Approval</v>
+        <v>User ARO melakukan input SONumber di Stip approval</v>
       </c>
       <c r="B2" t="str">
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-08-29T03:33:48.763Z</v>
+        <v>2025-09-01T02:36:36.421Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>User LEAD PM melakukan input SONumber di Stip approval</v>
+        <v>User ARO melakukan klik tombol Search di Stip approval</v>
       </c>
       <c r="B3" t="str">
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2025-08-29T03:33:57.176Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2025-08-29T03:33:57.375Z</v>
+        <v>2025-09-01T02:36:36.957Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
+++ b/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,48 +407,56 @@
         <v>Status</v>
       </c>
       <c r="C1" t="str">
-        <v>timeStamp</v>
-      </c>
-      <c r="D1" t="str">
         <v>Timestamp</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>User AM melakukan akses ke menu Project activity Header</v>
+        <v>Button Clicked</v>
       </c>
       <c r="B2" t="str">
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2025-12-19T03:06:19.054Z</v>
+        <v>2026-03-06T00:08:26.878Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
+        <v>User masuk ke Page Stip Input</v>
       </c>
       <c r="B3" t="str">
         <v>Pass</v>
       </c>
-      <c r="D3" t="str">
-        <v>2025-12-19T03:06:54.354Z</v>
+      <c r="C3" t="str">
+        <v>2026-03-06T00:08:26.879Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>User AM melakukan klik tombol Search di Stip approval</v>
+        <v>User ID Input</v>
       </c>
       <c r="B4" t="str">
         <v>Pass</v>
       </c>
-      <c r="D4" t="str">
-        <v>2025-12-19T03:06:54.553Z</v>
+      <c r="C4" t="str">
+        <v>2026-03-06T00:08:28.666Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Passworhasbeeninputed</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-03-06T00:08:28.941Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
+++ b/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,56 +407,34 @@
         <v>Status</v>
       </c>
       <c r="C1" t="str">
-        <v>Timestamp</v>
+        <v>TimeStamp</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Button Clicked</v>
+        <v>User ARO melakukan input SONumber di Stip approval</v>
       </c>
       <c r="B2" t="str">
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-06T00:08:26.878Z</v>
+        <v>2026-03-09T00:15:27.648Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>User masuk ke Page Stip Input</v>
+        <v>User ARO melakukan klik tombol Search di Stip approval</v>
       </c>
       <c r="B3" t="str">
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-06T00:08:26.879Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>User ID Input</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2026-03-06T00:08:28.666Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Passworhasbeeninputed</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Pass</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2026-03-06T00:08:28.941Z</v>
+        <v>2026-03-09T00:15:27.847Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
+++ b/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,34 +407,56 @@
         <v>Status</v>
       </c>
       <c r="C1" t="str">
-        <v>TimeStamp</v>
+        <v>Timestamp</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>User ARO melakukan input SONumber di Stip approval</v>
+        <v>Button Clicked</v>
       </c>
       <c r="B2" t="str">
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-03-09T00:15:27.648Z</v>
+        <v>2026-04-02T02:45:23.340Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>User ARO melakukan klik tombol Search di Stip approval</v>
+        <v>User masuk ke Page Stip Input</v>
       </c>
       <c r="B3" t="str">
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-03-09T00:15:27.847Z</v>
+        <v>2026-04-02T02:45:23.341Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>User ID Input</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-04-02T02:45:24.200Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Passworhasbeeninputed</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-04-02T02:45:24.448Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
+++ b/cypress/downloads/test-StipinputNewBuildMacroresults.xlsx
@@ -418,7 +418,7 @@
         <v>Pass</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-04-02T02:45:23.340Z</v>
+        <v>2026-04-02T07:34:55.464Z</v>
       </c>
     </row>
     <row r="3">
@@ -429,7 +429,7 @@
         <v>Pass</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-04-02T02:45:23.341Z</v>
+        <v>2026-04-02T07:34:55.464Z</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>Pass</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-04-02T02:45:24.200Z</v>
+        <v>2026-04-02T07:34:59.482Z</v>
       </c>
     </row>
     <row r="5">
@@ -451,7 +451,7 @@
         <v>Pass</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-04-02T02:45:24.448Z</v>
+        <v>2026-04-02T07:34:59.714Z</v>
       </c>
     </row>
   </sheetData>
